--- a/data/dsc_seedcane_chopping.xlsx
+++ b/data/dsc_seedcane_chopping.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t>Date</t>
   </si>
@@ -28,32 +33,113 @@
     <t>Choppers</t>
   </si>
   <si>
+    <t>Capitao</t>
+  </si>
+  <si>
+    <t>Dipper</t>
+  </si>
+  <si>
+    <t>B/Guard</t>
+  </si>
+  <si>
+    <t>First_Aider</t>
+  </si>
+  <si>
+    <t>SHEQ</t>
+  </si>
+  <si>
     <t>2025-07-01</t>
   </si>
   <si>
     <t>2025-07-02</t>
   </si>
   <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
     <t>2025-07-07</t>
   </si>
   <si>
-    <t>5612</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>121</t>
+    <t>2025-06-27</t>
+  </si>
+  <si>
+    <t>2025-06-28</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>2025-07-04</t>
+  </si>
+  <si>
+    <t>2025-07-05</t>
+  </si>
+  <si>
+    <t>2025-07-08</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>2025-07-10</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>2025-07-12</t>
+  </si>
+  <si>
+    <t>2025-07-13</t>
+  </si>
+  <si>
+    <t>2025-07-14</t>
+  </si>
+  <si>
+    <t>2025-07-15</t>
+  </si>
+  <si>
+    <t>2025-07-16</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>2025-07-18</t>
+  </si>
+  <si>
+    <t>2025-07-22</t>
+  </si>
+  <si>
+    <t>2025-07-23</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,6 +202,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -162,7 +256,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -194,9 +288,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -228,6 +323,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -403,11 +499,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,61 +519,1209 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>5852</v>
+      </c>
+      <c r="C2">
+        <v>47</v>
+      </c>
+      <c r="D2">
+        <v>110</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>5853</v>
+      </c>
+      <c r="C3">
+        <v>32</v>
+      </c>
+      <c r="D3">
+        <v>99</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>5854</v>
+      </c>
+      <c r="C4">
+        <v>33</v>
+      </c>
+      <c r="D4">
+        <v>91</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>5831</v>
+      </c>
+      <c r="C5">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>39</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>5831</v>
+      </c>
+      <c r="C6">
+        <v>30</v>
+      </c>
+      <c r="D6">
+        <v>86</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>5834</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>65</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>5832</v>
+      </c>
+      <c r="C8">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>5832</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>18</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
         <v>5454</v>
       </c>
-      <c r="C2">
-        <v>60</v>
-      </c>
-      <c r="D2">
+      <c r="C10">
+        <v>27</v>
+      </c>
+      <c r="D10">
+        <v>48</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>5611</v>
+      </c>
+      <c r="C11">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>28</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>5612</v>
+      </c>
+      <c r="C12">
+        <v>64</v>
+      </c>
+      <c r="D12">
+        <v>158</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>5612</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13">
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>5613</v>
+      </c>
+      <c r="C14">
+        <v>31</v>
+      </c>
+      <c r="D14">
+        <v>64</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>5612</v>
+      </c>
+      <c r="C15">
+        <v>22</v>
+      </c>
+      <c r="D15">
+        <v>40</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>2106</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+      <c r="D16">
+        <v>43</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17">
+        <v>5613</v>
+      </c>
+      <c r="C17">
+        <v>27</v>
+      </c>
+      <c r="D17">
+        <v>61</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <v>5492</v>
+      </c>
+      <c r="C18">
+        <v>21</v>
+      </c>
+      <c r="D18">
+        <v>48</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19">
+        <v>5219</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>43</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>2106</v>
+      </c>
+      <c r="C20">
+        <v>19</v>
+      </c>
+      <c r="D20">
+        <v>30</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21">
+        <v>5492</v>
+      </c>
+      <c r="C21">
+        <v>37</v>
+      </c>
+      <c r="D21">
+        <v>80</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22">
+        <v>2106</v>
+      </c>
+      <c r="C22">
+        <v>18</v>
+      </c>
+      <c r="D22">
+        <v>32</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23">
+        <v>5442</v>
+      </c>
+      <c r="C23">
+        <v>17</v>
+      </c>
+      <c r="D23">
+        <v>36</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24">
+        <v>5812</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>6</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>5418</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>12</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>5848</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>9</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>5442</v>
+      </c>
+      <c r="C27">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <v>26</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>5442</v>
+      </c>
+      <c r="C28">
+        <v>21</v>
+      </c>
+      <c r="D28">
+        <v>42</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>2106</v>
+      </c>
+      <c r="C29">
+        <v>7</v>
+      </c>
+      <c r="D29">
+        <v>19</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>5442</v>
+      </c>
+      <c r="C30">
+        <v>6</v>
+      </c>
+      <c r="D30">
+        <v>13</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31">
+        <v>5418</v>
+      </c>
+      <c r="C31">
+        <v>13</v>
+      </c>
+      <c r="D31">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>5454</v>
-      </c>
-      <c r="C3">
-        <v>20</v>
-      </c>
-      <c r="D3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32">
+        <v>5843</v>
+      </c>
+      <c r="C32">
+        <v>8</v>
+      </c>
+      <c r="D32">
+        <v>21</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33">
+        <v>2106</v>
+      </c>
+      <c r="C33">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>5612</v>
-      </c>
-      <c r="C4">
-        <v>60</v>
-      </c>
-      <c r="D4">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="D33">
+        <v>11</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34">
+        <v>2106</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34">
+        <v>10</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35">
+        <v>5418</v>
+      </c>
+      <c r="C35">
+        <v>14</v>
+      </c>
+      <c r="D35">
+        <v>57</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36">
+        <v>5414</v>
+      </c>
+      <c r="C36">
+        <v>33</v>
+      </c>
+      <c r="D36">
+        <v>58</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37">
+        <v>5418</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38">
+        <v>3314</v>
+      </c>
+      <c r="C38">
+        <v>29</v>
+      </c>
+      <c r="D38">
+        <v>69</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39">
+        <v>5418</v>
+      </c>
+      <c r="C39">
+        <v>17</v>
+      </c>
+      <c r="D39">
+        <v>39</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40">
+        <v>3314</v>
+      </c>
+      <c r="C40">
+        <v>16</v>
+      </c>
+      <c r="D40">
+        <v>57</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41">
+        <v>5418</v>
+      </c>
+      <c r="C41">
+        <v>7</v>
+      </c>
+      <c r="D41">
+        <v>23</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" t="s">
+        <v>37</v>
+      </c>
+      <c r="F42" t="s">
+        <v>37</v>
+      </c>
+      <c r="G42" t="s">
+        <v>37</v>
+      </c>
+      <c r="H42" t="s">
+        <v>37</v>
+      </c>
+      <c r="I42" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/dsc_seedcane_chopping.xlsx
+++ b/data/dsc_seedcane_chopping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="171">
   <si>
     <t>Date</t>
   </si>
@@ -187,6 +187,174 @@
     <t>2025-07-31</t>
   </si>
   <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>2025-08-02</t>
+  </si>
+  <si>
+    <t>2025-08-03</t>
+  </si>
+  <si>
+    <t>2025-08-04</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>2025-08-09</t>
+  </si>
+  <si>
+    <t>2025-08-10</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>2025-08-12</t>
+  </si>
+  <si>
+    <t>2025-08-13</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>2025-08-15</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>2025-08-20</t>
+  </si>
+  <si>
+    <t>2025-08-21</t>
+  </si>
+  <si>
+    <t>2025-08-22</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>2025-08-24</t>
+  </si>
+  <si>
+    <t>2025-08-25</t>
+  </si>
+  <si>
+    <t>2025-08-26</t>
+  </si>
+  <si>
+    <t>2025-08-27</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>2025-08-29</t>
+  </si>
+  <si>
+    <t>2025-08-30</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
+    <t>2025-09-03</t>
+  </si>
+  <si>
+    <t>2025-09-04</t>
+  </si>
+  <si>
+    <t>2025-09-06</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>2025-09-08</t>
+  </si>
+  <si>
+    <t>2025-09-09</t>
+  </si>
+  <si>
+    <t>2025-09-10</t>
+  </si>
+  <si>
+    <t>2025-09-11</t>
+  </si>
+  <si>
+    <t>2025-09-12</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>2025-09-17</t>
+  </si>
+  <si>
+    <t>2025-09-18</t>
+  </si>
+  <si>
+    <t>2025-09-19</t>
+  </si>
+  <si>
+    <t>2025-09-21</t>
+  </si>
+  <si>
+    <t>2025-09-23</t>
+  </si>
+  <si>
+    <t>2025-09-24</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>2025-10-07</t>
+  </si>
+  <si>
+    <t>2025-10-10</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>2025-10-12</t>
+  </si>
+  <si>
+    <t>2025-10-13</t>
+  </si>
+  <si>
+    <t>2025-10-14</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>2025-10-16</t>
+  </si>
+  <si>
     <t>5414C</t>
   </si>
   <si>
@@ -205,10 +373,154 @@
     <t>5842</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>5824</t>
+  </si>
+  <si>
+    <t>5823</t>
+  </si>
+  <si>
+    <t>5439</t>
+  </si>
+  <si>
+    <t>5429</t>
+  </si>
+  <si>
+    <t>5814</t>
+  </si>
+  <si>
+    <t>5822</t>
+  </si>
+  <si>
+    <t>5841</t>
+  </si>
+  <si>
+    <t>5417</t>
+  </si>
+  <si>
+    <t>5445</t>
+  </si>
+  <si>
+    <t>5445, 5449</t>
+  </si>
+  <si>
+    <t>5506</t>
+  </si>
+  <si>
+    <t>5405</t>
+  </si>
+  <si>
+    <t>5501</t>
+  </si>
+  <si>
+    <t>5612</t>
+  </si>
+  <si>
+    <t>5405B</t>
+  </si>
+  <si>
+    <t>5405C</t>
+  </si>
+  <si>
+    <t>5844</t>
+  </si>
+  <si>
+    <t>5833</t>
+  </si>
+  <si>
+    <t>5611</t>
+  </si>
+  <si>
+    <t>5821</t>
+  </si>
+  <si>
+    <t>5831</t>
+  </si>
+  <si>
+    <t>5834</t>
+  </si>
+  <si>
+    <t>5447</t>
+  </si>
+  <si>
+    <t>5854</t>
+  </si>
+  <si>
+    <t>5852</t>
+  </si>
+  <si>
+    <t>5455</t>
+  </si>
+  <si>
+    <t>5492</t>
+  </si>
+  <si>
+    <t>5851</t>
+  </si>
+  <si>
+    <t>5832</t>
+  </si>
+  <si>
+    <t>5410</t>
+  </si>
+  <si>
+    <t>5663</t>
+  </si>
+  <si>
+    <t>5613</t>
+  </si>
+  <si>
+    <t>5614</t>
+  </si>
+  <si>
+    <t>5664</t>
+  </si>
+  <si>
+    <t>5208</t>
+  </si>
+  <si>
+    <t>5437</t>
+  </si>
+  <si>
+    <t>5418</t>
+  </si>
+  <si>
+    <t>5219</t>
+  </si>
+  <si>
+    <t>5601</t>
+  </si>
+  <si>
+    <t>5458</t>
+  </si>
+  <si>
+    <t>5406</t>
+  </si>
+  <si>
+    <t>5106</t>
+  </si>
+  <si>
+    <t>5217</t>
+  </si>
+  <si>
+    <t>5213</t>
+  </si>
+  <si>
+    <t>5491</t>
+  </si>
+  <si>
+    <t>5201</t>
+  </si>
+  <si>
+    <t>5202</t>
+  </si>
+  <si>
+    <t>5449</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>1</t>
@@ -572,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2755,7 +3067,7 @@
         <v>55</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="C76">
         <v>10</v>
@@ -2784,7 +3096,7 @@
         <v>55</v>
       </c>
       <c r="B77" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="C77">
         <v>3</v>
@@ -2813,7 +3125,7 @@
         <v>55</v>
       </c>
       <c r="B78" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="C78">
         <v>3</v>
@@ -2842,7 +3154,7 @@
         <v>55</v>
       </c>
       <c r="B79" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="C79">
         <v>3</v>
@@ -2871,7 +3183,7 @@
         <v>56</v>
       </c>
       <c r="B80" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="C80">
         <v>28</v>
@@ -2900,7 +3212,7 @@
         <v>56</v>
       </c>
       <c r="B81" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="C81">
         <v>4</v>
@@ -2929,28 +3241,4465 @@
         <v>56</v>
       </c>
       <c r="B82" t="s">
+        <v>118</v>
+      </c>
+      <c r="C82">
+        <v>7</v>
+      </c>
+      <c r="D82">
+        <v>15</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>57</v>
+      </c>
+      <c r="B83" t="s">
+        <v>116</v>
+      </c>
+      <c r="C83">
+        <v>28</v>
+      </c>
+      <c r="D83">
+        <v>60</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>57</v>
+      </c>
+      <c r="B84" t="s">
+        <v>119</v>
+      </c>
+      <c r="C84">
+        <v>5</v>
+      </c>
+      <c r="D84">
+        <v>15</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" t="s">
+        <v>57</v>
+      </c>
+      <c r="B85" t="s">
+        <v>120</v>
+      </c>
+      <c r="C85">
+        <v>7</v>
+      </c>
+      <c r="D85">
+        <v>9</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" t="s">
+        <v>57</v>
+      </c>
+      <c r="B86" t="s">
+        <v>117</v>
+      </c>
+      <c r="C86">
+        <v>4</v>
+      </c>
+      <c r="D86">
+        <v>4</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" t="s">
+        <v>57</v>
+      </c>
+      <c r="B87" t="s">
+        <v>114</v>
+      </c>
+      <c r="C87">
+        <v>3</v>
+      </c>
+      <c r="D87">
+        <v>3</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" t="s">
+        <v>58</v>
+      </c>
+      <c r="B88" t="s">
+        <v>121</v>
+      </c>
+      <c r="C88">
+        <v>22</v>
+      </c>
+      <c r="D88">
+        <v>56</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" t="s">
+        <v>58</v>
+      </c>
+      <c r="B89" t="s">
+        <v>120</v>
+      </c>
+      <c r="C89">
+        <v>3</v>
+      </c>
+      <c r="D89">
+        <v>6</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" t="s">
+        <v>58</v>
+      </c>
+      <c r="B90" t="s">
+        <v>114</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90">
+        <v>4</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" t="s">
+        <v>58</v>
+      </c>
+      <c r="B91" t="s">
+        <v>117</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91">
+        <v>6</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" t="s">
+        <v>59</v>
+      </c>
+      <c r="B92" t="s">
+        <v>122</v>
+      </c>
+      <c r="C92">
+        <v>11</v>
+      </c>
+      <c r="D92">
+        <v>33</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" t="s">
+        <v>59</v>
+      </c>
+      <c r="B93" t="s">
+        <v>123</v>
+      </c>
+      <c r="C93">
+        <v>3</v>
+      </c>
+      <c r="D93">
+        <v>6</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" t="s">
+        <v>59</v>
+      </c>
+      <c r="B94" t="s">
+        <v>124</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94">
+        <v>6</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" t="s">
+        <v>59</v>
+      </c>
+      <c r="B95" t="s">
+        <v>119</v>
+      </c>
+      <c r="C95">
+        <v>3</v>
+      </c>
+      <c r="D95">
+        <v>6</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" t="s">
+        <v>60</v>
+      </c>
+      <c r="B96" t="s">
+        <v>121</v>
+      </c>
+      <c r="C96">
+        <v>11</v>
+      </c>
+      <c r="D96">
+        <v>30</v>
+      </c>
+      <c r="E96">
+        <v>3</v>
+      </c>
+      <c r="F96">
+        <v>2</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" t="s">
+        <v>61</v>
+      </c>
+      <c r="B97" t="s">
+        <v>118</v>
+      </c>
+      <c r="C97">
+        <v>15</v>
+      </c>
+      <c r="D97">
+        <v>33</v>
+      </c>
+      <c r="E97">
+        <v>2</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" t="s">
+        <v>61</v>
+      </c>
+      <c r="B98" t="s">
+        <v>125</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>2</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" t="s">
+        <v>61</v>
+      </c>
+      <c r="B99" t="s">
+        <v>119</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99">
+        <v>3</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" t="s">
         <v>62</v>
       </c>
-      <c r="C82" t="s">
+      <c r="B100" t="s">
+        <v>126</v>
+      </c>
+      <c r="C100">
+        <v>31</v>
+      </c>
+      <c r="D100">
+        <v>75</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="F100">
+        <v>2</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" t="s">
         <v>63</v>
       </c>
-      <c r="D82" t="s">
+      <c r="B101" t="s">
+        <v>126</v>
+      </c>
+      <c r="C101">
+        <v>16</v>
+      </c>
+      <c r="D101">
+        <v>39</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" t="s">
         <v>64</v>
       </c>
-      <c r="E82" t="s">
+      <c r="B102" t="s">
+        <v>126</v>
+      </c>
+      <c r="C102">
+        <v>13</v>
+      </c>
+      <c r="D102">
+        <v>37</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" t="s">
+        <v>64</v>
+      </c>
+      <c r="B103" t="s">
+        <v>127</v>
+      </c>
+      <c r="C103">
+        <v>31</v>
+      </c>
+      <c r="D103">
+        <v>45</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" t="s">
         <v>65</v>
       </c>
-      <c r="F82" t="s">
+      <c r="B104" t="s">
+        <v>126</v>
+      </c>
+      <c r="C104">
+        <v>9</v>
+      </c>
+      <c r="D104">
+        <v>18</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" t="s">
         <v>65</v>
       </c>
-      <c r="G82" t="s">
-        <v>65</v>
-      </c>
-      <c r="H82" t="s">
+      <c r="B105" t="s">
+        <v>127</v>
+      </c>
+      <c r="C105">
+        <v>6</v>
+      </c>
+      <c r="D105">
+        <v>16</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" t="s">
         <v>66</v>
       </c>
-      <c r="I82" t="s">
-        <v>66</v>
+      <c r="B106" t="s">
+        <v>128</v>
+      </c>
+      <c r="C106">
+        <v>11</v>
+      </c>
+      <c r="D106">
+        <v>34</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="F106">
+        <v>2</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" t="s">
+        <v>67</v>
+      </c>
+      <c r="B107" t="s">
+        <v>129</v>
+      </c>
+      <c r="C107">
+        <v>15</v>
+      </c>
+      <c r="D107">
+        <v>35</v>
+      </c>
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" t="s">
+        <v>68</v>
+      </c>
+      <c r="B108" t="s">
+        <v>129</v>
+      </c>
+      <c r="C108">
+        <v>27</v>
+      </c>
+      <c r="D108">
+        <v>63</v>
+      </c>
+      <c r="E108">
+        <v>2</v>
+      </c>
+      <c r="F108">
+        <v>2</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" t="s">
+        <v>69</v>
+      </c>
+      <c r="B109" t="s">
+        <v>129</v>
+      </c>
+      <c r="C109">
+        <v>30</v>
+      </c>
+      <c r="D109">
+        <v>76</v>
+      </c>
+      <c r="E109">
+        <v>2</v>
+      </c>
+      <c r="F109">
+        <v>2</v>
+      </c>
+      <c r="G109">
+        <v>1</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" t="s">
+        <v>70</v>
+      </c>
+      <c r="B110" t="s">
+        <v>129</v>
+      </c>
+      <c r="C110">
+        <v>15</v>
+      </c>
+      <c r="D110">
+        <v>46</v>
+      </c>
+      <c r="E110">
+        <v>2</v>
+      </c>
+      <c r="F110">
+        <v>2</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" t="s">
+        <v>71</v>
+      </c>
+      <c r="B111" t="s">
+        <v>130</v>
+      </c>
+      <c r="C111">
+        <v>13</v>
+      </c>
+      <c r="D111">
+        <v>21</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" t="s">
+        <v>72</v>
+      </c>
+      <c r="B112" t="s">
+        <v>130</v>
+      </c>
+      <c r="C112">
+        <v>5</v>
+      </c>
+      <c r="D112">
+        <v>15</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" t="s">
+        <v>72</v>
+      </c>
+      <c r="B113" t="s">
+        <v>131</v>
+      </c>
+      <c r="C113">
+        <v>11</v>
+      </c>
+      <c r="D113">
+        <v>33</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="G113">
+        <v>1</v>
+      </c>
+      <c r="H113">
+        <v>1</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" t="s">
+        <v>73</v>
+      </c>
+      <c r="B114" t="s">
+        <v>131</v>
+      </c>
+      <c r="C114">
+        <v>18</v>
+      </c>
+      <c r="D114">
+        <v>40</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" t="s">
+        <v>73</v>
+      </c>
+      <c r="B115" t="s">
+        <v>130</v>
+      </c>
+      <c r="C115">
+        <v>12</v>
+      </c>
+      <c r="D115">
+        <v>26</v>
+      </c>
+      <c r="E115">
+        <v>2</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115">
+        <v>1</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" t="s">
+        <v>73</v>
+      </c>
+      <c r="B116" t="s">
+        <v>132</v>
+      </c>
+      <c r="C116">
+        <v>6</v>
+      </c>
+      <c r="D116">
+        <v>12</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" t="s">
+        <v>74</v>
+      </c>
+      <c r="B117" t="s">
+        <v>133</v>
+      </c>
+      <c r="C117">
+        <v>14</v>
+      </c>
+      <c r="D117">
+        <v>32</v>
+      </c>
+      <c r="E117">
+        <v>1</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117">
+        <v>1</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" t="s">
+        <v>74</v>
+      </c>
+      <c r="B118" t="s">
+        <v>134</v>
+      </c>
+      <c r="C118">
+        <v>9</v>
+      </c>
+      <c r="D118">
+        <v>15</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118">
+        <v>1</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" t="s">
+        <v>74</v>
+      </c>
+      <c r="B119" t="s">
+        <v>132</v>
+      </c>
+      <c r="C119">
+        <v>3</v>
+      </c>
+      <c r="D119">
+        <v>6</v>
+      </c>
+      <c r="E119">
+        <v>1</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" t="s">
+        <v>74</v>
+      </c>
+      <c r="B120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C120">
+        <v>13</v>
+      </c>
+      <c r="D120">
+        <v>35</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" t="s">
+        <v>75</v>
+      </c>
+      <c r="B121" t="s">
+        <v>130</v>
+      </c>
+      <c r="C121">
+        <v>18</v>
+      </c>
+      <c r="D121">
+        <v>50</v>
+      </c>
+      <c r="E121">
+        <v>2</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121">
+        <v>1</v>
+      </c>
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" t="s">
+        <v>75</v>
+      </c>
+      <c r="B122" t="s">
+        <v>131</v>
+      </c>
+      <c r="C122">
+        <v>8</v>
+      </c>
+      <c r="D122">
+        <v>32</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+      <c r="H122">
+        <v>1</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" t="s">
+        <v>76</v>
+      </c>
+      <c r="B123" t="s">
+        <v>130</v>
+      </c>
+      <c r="C123">
+        <v>21</v>
+      </c>
+      <c r="D123">
+        <v>47</v>
+      </c>
+      <c r="E123">
+        <v>2</v>
+      </c>
+      <c r="F123">
+        <v>2</v>
+      </c>
+      <c r="G123">
+        <v>2</v>
+      </c>
+      <c r="H123">
+        <v>1</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" t="s">
+        <v>77</v>
+      </c>
+      <c r="B124" t="s">
+        <v>135</v>
+      </c>
+      <c r="C124">
+        <v>11</v>
+      </c>
+      <c r="D124">
+        <v>33</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" t="s">
+        <v>77</v>
+      </c>
+      <c r="B125" t="s">
+        <v>132</v>
+      </c>
+      <c r="C125">
+        <v>2</v>
+      </c>
+      <c r="D125">
+        <v>6</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" t="s">
+        <v>77</v>
+      </c>
+      <c r="B126" t="s">
+        <v>136</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+      <c r="D126">
+        <v>3</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" t="s">
+        <v>78</v>
+      </c>
+      <c r="B127" t="s">
+        <v>130</v>
+      </c>
+      <c r="C127">
+        <v>3</v>
+      </c>
+      <c r="D127">
+        <v>10</v>
+      </c>
+      <c r="E127">
+        <v>2</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>1</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" t="s">
+        <v>79</v>
+      </c>
+      <c r="B128" t="s">
+        <v>123</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128">
+        <v>4</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" t="s">
+        <v>80</v>
+      </c>
+      <c r="B129" t="s">
+        <v>137</v>
+      </c>
+      <c r="C129">
+        <v>6</v>
+      </c>
+      <c r="D129">
+        <v>12</v>
+      </c>
+      <c r="E129">
+        <v>1</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" t="s">
+        <v>80</v>
+      </c>
+      <c r="B130" t="s">
+        <v>138</v>
+      </c>
+      <c r="C130">
+        <v>5</v>
+      </c>
+      <c r="D130">
+        <v>11</v>
+      </c>
+      <c r="E130">
+        <v>1</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" t="s">
+        <v>80</v>
+      </c>
+      <c r="B131" t="s">
+        <v>139</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131">
+        <v>2</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" t="s">
+        <v>80</v>
+      </c>
+      <c r="B132" t="s">
+        <v>140</v>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+      <c r="D132">
+        <v>4</v>
+      </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" t="s">
+        <v>80</v>
+      </c>
+      <c r="B133" t="s">
+        <v>123</v>
+      </c>
+      <c r="C133">
+        <v>3</v>
+      </c>
+      <c r="D133">
+        <v>8</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" t="s">
+        <v>81</v>
+      </c>
+      <c r="B134" t="s">
+        <v>141</v>
+      </c>
+      <c r="C134">
+        <v>5</v>
+      </c>
+      <c r="D134">
+        <v>25</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134">
+        <v>1</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" t="s">
+        <v>81</v>
+      </c>
+      <c r="B135" t="s">
+        <v>137</v>
+      </c>
+      <c r="C135">
+        <v>12</v>
+      </c>
+      <c r="D135">
+        <v>36</v>
+      </c>
+      <c r="E135">
+        <v>2</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135">
+        <v>1</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" t="s">
+        <v>82</v>
+      </c>
+      <c r="B136" t="s">
+        <v>132</v>
+      </c>
+      <c r="C136">
+        <v>3</v>
+      </c>
+      <c r="D136">
+        <v>8</v>
+      </c>
+      <c r="E136">
+        <v>1</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136">
+        <v>2</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" t="s">
+        <v>83</v>
+      </c>
+      <c r="B137" t="s">
+        <v>142</v>
+      </c>
+      <c r="C137">
+        <v>8</v>
+      </c>
+      <c r="D137">
+        <v>22</v>
+      </c>
+      <c r="E137">
+        <v>2</v>
+      </c>
+      <c r="F137">
+        <v>2</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" t="s">
+        <v>84</v>
+      </c>
+      <c r="B138" t="s">
+        <v>142</v>
+      </c>
+      <c r="C138">
+        <v>13</v>
+      </c>
+      <c r="D138">
+        <v>26</v>
+      </c>
+      <c r="E138">
+        <v>3</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" t="s">
+        <v>84</v>
+      </c>
+      <c r="B139" t="s">
+        <v>143</v>
+      </c>
+      <c r="C139">
+        <v>3</v>
+      </c>
+      <c r="D139">
+        <v>8</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="G139">
+        <v>1</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" t="s">
+        <v>84</v>
+      </c>
+      <c r="B140" t="s">
+        <v>118</v>
+      </c>
+      <c r="C140">
+        <v>2</v>
+      </c>
+      <c r="D140">
+        <v>6</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" t="s">
+        <v>85</v>
+      </c>
+      <c r="B141" t="s">
+        <v>124</v>
+      </c>
+      <c r="C141">
+        <v>4</v>
+      </c>
+      <c r="D141">
+        <v>10</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
+      </c>
+      <c r="F141">
+        <v>2</v>
+      </c>
+      <c r="G141">
+        <v>1</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+      <c r="I141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" t="s">
+        <v>85</v>
+      </c>
+      <c r="B142" t="s">
+        <v>142</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+      <c r="D142">
+        <v>4</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" t="s">
+        <v>85</v>
+      </c>
+      <c r="B143" t="s">
+        <v>139</v>
+      </c>
+      <c r="C143">
+        <v>2</v>
+      </c>
+      <c r="D143">
+        <v>4</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" t="s">
+        <v>86</v>
+      </c>
+      <c r="B144" t="s">
+        <v>120</v>
+      </c>
+      <c r="C144">
+        <v>7</v>
+      </c>
+      <c r="D144">
+        <v>21</v>
+      </c>
+      <c r="E144">
+        <v>2</v>
+      </c>
+      <c r="F144">
+        <v>3</v>
+      </c>
+      <c r="G144">
+        <v>1</v>
+      </c>
+      <c r="H144">
+        <v>1</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" t="s">
+        <v>86</v>
+      </c>
+      <c r="B145" t="s">
+        <v>138</v>
+      </c>
+      <c r="C145">
+        <v>2</v>
+      </c>
+      <c r="D145">
+        <v>5</v>
+      </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" t="s">
+        <v>86</v>
+      </c>
+      <c r="B146" t="s">
+        <v>143</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146">
+        <v>3</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" t="s">
+        <v>86</v>
+      </c>
+      <c r="B147" t="s">
+        <v>124</v>
+      </c>
+      <c r="C147">
+        <v>8</v>
+      </c>
+      <c r="D147">
+        <v>24</v>
+      </c>
+      <c r="E147">
+        <v>2</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+      <c r="G147">
+        <v>1</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" t="s">
+        <v>87</v>
+      </c>
+      <c r="B148" t="s">
+        <v>124</v>
+      </c>
+      <c r="C148">
+        <v>4</v>
+      </c>
+      <c r="D148">
+        <v>12</v>
+      </c>
+      <c r="E148">
+        <v>1</v>
+      </c>
+      <c r="F148">
+        <v>2</v>
+      </c>
+      <c r="G148">
+        <v>1</v>
+      </c>
+      <c r="H148">
+        <v>1</v>
+      </c>
+      <c r="I148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" t="s">
+        <v>87</v>
+      </c>
+      <c r="B149" t="s">
+        <v>140</v>
+      </c>
+      <c r="C149">
+        <v>6</v>
+      </c>
+      <c r="D149">
+        <v>18</v>
+      </c>
+      <c r="E149">
+        <v>2</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>1</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" t="s">
+        <v>88</v>
+      </c>
+      <c r="B150" t="s">
+        <v>144</v>
+      </c>
+      <c r="C150">
+        <v>14</v>
+      </c>
+      <c r="D150">
+        <v>46</v>
+      </c>
+      <c r="E150">
+        <v>2</v>
+      </c>
+      <c r="F150">
+        <v>1</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>1</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" t="s">
+        <v>88</v>
+      </c>
+      <c r="B151" t="s">
+        <v>119</v>
+      </c>
+      <c r="C151">
+        <v>2</v>
+      </c>
+      <c r="D151">
+        <v>6</v>
+      </c>
+      <c r="E151">
+        <v>1</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+      <c r="I151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" t="s">
+        <v>88</v>
+      </c>
+      <c r="B152" t="s">
+        <v>145</v>
+      </c>
+      <c r="C152">
+        <v>2</v>
+      </c>
+      <c r="D152">
+        <v>6</v>
+      </c>
+      <c r="E152">
+        <v>0</v>
+      </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" t="s">
+        <v>88</v>
+      </c>
+      <c r="B153" t="s">
+        <v>135</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+      <c r="D153">
+        <v>4</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+      <c r="F153">
+        <v>0</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" t="s">
+        <v>88</v>
+      </c>
+      <c r="B154" t="s">
+        <v>146</v>
+      </c>
+      <c r="C154">
+        <v>2</v>
+      </c>
+      <c r="D154">
+        <v>6</v>
+      </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" t="s">
+        <v>88</v>
+      </c>
+      <c r="B155" t="s">
+        <v>147</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="D155">
+        <v>3</v>
+      </c>
+      <c r="E155">
+        <v>0</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" t="s">
+        <v>88</v>
+      </c>
+      <c r="B156" t="s">
+        <v>148</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+      <c r="D156">
+        <v>3</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" t="s">
+        <v>88</v>
+      </c>
+      <c r="B157" t="s">
+        <v>148</v>
+      </c>
+      <c r="C157">
+        <v>1</v>
+      </c>
+      <c r="D157">
+        <v>3</v>
+      </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
+      <c r="F157">
+        <v>0</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158" t="s">
+        <v>88</v>
+      </c>
+      <c r="B158" t="s">
+        <v>145</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="D158">
+        <v>3</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" t="s">
+        <v>88</v>
+      </c>
+      <c r="B159" t="s">
+        <v>119</v>
+      </c>
+      <c r="C159">
+        <v>5</v>
+      </c>
+      <c r="D159">
+        <v>15</v>
+      </c>
+      <c r="E159">
+        <v>1</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" t="s">
+        <v>88</v>
+      </c>
+      <c r="B160" t="s">
+        <v>149</v>
+      </c>
+      <c r="C160">
+        <v>6</v>
+      </c>
+      <c r="D160">
+        <v>18</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161" t="s">
+        <v>89</v>
+      </c>
+      <c r="B161" t="s">
+        <v>144</v>
+      </c>
+      <c r="C161">
+        <v>3</v>
+      </c>
+      <c r="D161">
+        <v>9</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161">
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <v>1</v>
+      </c>
+      <c r="I161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" t="s">
+        <v>89</v>
+      </c>
+      <c r="B162" t="s">
+        <v>150</v>
+      </c>
+      <c r="C162">
+        <v>6</v>
+      </c>
+      <c r="D162">
+        <v>18</v>
+      </c>
+      <c r="E162">
+        <v>1</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>1</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" t="s">
+        <v>89</v>
+      </c>
+      <c r="B163" t="s">
+        <v>151</v>
+      </c>
+      <c r="C163">
+        <v>9</v>
+      </c>
+      <c r="D163">
+        <v>27</v>
+      </c>
+      <c r="E163">
+        <v>1</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>1</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" t="s">
+        <v>90</v>
+      </c>
+      <c r="B164" t="s">
+        <v>149</v>
+      </c>
+      <c r="C164">
+        <v>4</v>
+      </c>
+      <c r="D164">
+        <v>12</v>
+      </c>
+      <c r="E164">
+        <v>0</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+      <c r="G164">
+        <v>1</v>
+      </c>
+      <c r="H164">
+        <v>1</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" t="s">
+        <v>90</v>
+      </c>
+      <c r="B165" t="s">
+        <v>152</v>
+      </c>
+      <c r="C165">
+        <v>3</v>
+      </c>
+      <c r="D165">
+        <v>9</v>
+      </c>
+      <c r="E165">
+        <v>1</v>
+      </c>
+      <c r="F165">
+        <v>0</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166" t="s">
+        <v>91</v>
+      </c>
+      <c r="B166" t="s">
+        <v>144</v>
+      </c>
+      <c r="C166">
+        <v>7</v>
+      </c>
+      <c r="D166">
+        <v>23</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
+      </c>
+      <c r="F166">
+        <v>2</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+      <c r="H166">
+        <v>1</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167" t="s">
+        <v>91</v>
+      </c>
+      <c r="B167" t="s">
+        <v>120</v>
+      </c>
+      <c r="C167">
+        <v>2</v>
+      </c>
+      <c r="D167">
+        <v>7</v>
+      </c>
+      <c r="E167">
+        <v>1</v>
+      </c>
+      <c r="F167">
+        <v>2</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168" t="s">
+        <v>91</v>
+      </c>
+      <c r="B168" t="s">
+        <v>153</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+      <c r="D168">
+        <v>3</v>
+      </c>
+      <c r="E168">
+        <v>1</v>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" t="s">
+        <v>91</v>
+      </c>
+      <c r="B169" t="s">
+        <v>126</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="D169">
+        <v>3</v>
+      </c>
+      <c r="E169">
+        <v>0</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" t="s">
+        <v>91</v>
+      </c>
+      <c r="B170" t="s">
+        <v>154</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="D170">
+        <v>3</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" t="s">
+        <v>92</v>
+      </c>
+      <c r="B171" t="s">
+        <v>140</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171">
+        <v>3</v>
+      </c>
+      <c r="E171">
+        <v>1</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
+      <c r="A172" t="s">
+        <v>92</v>
+      </c>
+      <c r="B172" t="s">
+        <v>136</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="D172">
+        <v>3</v>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+      <c r="F172">
+        <v>0</v>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
+      <c r="A173" t="s">
+        <v>92</v>
+      </c>
+      <c r="B173" t="s">
+        <v>145</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173">
+        <v>1</v>
+      </c>
+      <c r="E173">
+        <v>3</v>
+      </c>
+      <c r="F173">
+        <v>0</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="A174" t="s">
+        <v>92</v>
+      </c>
+      <c r="B174" t="s">
+        <v>148</v>
+      </c>
+      <c r="C174">
+        <v>1</v>
+      </c>
+      <c r="D174">
+        <v>4</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
+      <c r="F174">
+        <v>0</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
+      <c r="A175" t="s">
+        <v>92</v>
+      </c>
+      <c r="B175" t="s">
+        <v>125</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+      <c r="D175">
+        <v>3</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+      <c r="F175">
+        <v>0</v>
+      </c>
+      <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
+      <c r="A176" t="s">
+        <v>92</v>
+      </c>
+      <c r="B176" t="s">
+        <v>144</v>
+      </c>
+      <c r="C176">
+        <v>4</v>
+      </c>
+      <c r="D176">
+        <v>13</v>
+      </c>
+      <c r="E176">
+        <v>1</v>
+      </c>
+      <c r="F176">
+        <v>1</v>
+      </c>
+      <c r="G176">
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
+      <c r="A177" t="s">
+        <v>93</v>
+      </c>
+      <c r="B177" t="s">
+        <v>136</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+      <c r="D177">
+        <v>3</v>
+      </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
+      <c r="F177">
+        <v>1</v>
+      </c>
+      <c r="G177">
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
+      <c r="A178" t="s">
+        <v>93</v>
+      </c>
+      <c r="B178" t="s">
+        <v>144</v>
+      </c>
+      <c r="C178">
+        <v>4</v>
+      </c>
+      <c r="D178">
+        <v>13</v>
+      </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
+      <c r="F178">
+        <v>1</v>
+      </c>
+      <c r="G178">
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
+      <c r="A179" t="s">
+        <v>93</v>
+      </c>
+      <c r="B179" t="s">
+        <v>139</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179">
+        <v>3</v>
+      </c>
+      <c r="E179">
+        <v>0</v>
+      </c>
+      <c r="F179">
+        <v>1</v>
+      </c>
+      <c r="G179">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
+      <c r="A180" t="s">
+        <v>93</v>
+      </c>
+      <c r="B180" t="s">
+        <v>124</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180">
+        <v>3</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
+      <c r="A181" t="s">
+        <v>93</v>
+      </c>
+      <c r="B181" t="s">
+        <v>154</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+      <c r="D181">
+        <v>3</v>
+      </c>
+      <c r="E181">
+        <v>0</v>
+      </c>
+      <c r="F181">
+        <v>1</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
+      <c r="A182" t="s">
+        <v>94</v>
+      </c>
+      <c r="B182" t="s">
+        <v>140</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182">
+        <v>3</v>
+      </c>
+      <c r="E182">
+        <v>0</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
+      <c r="A183" t="s">
+        <v>94</v>
+      </c>
+      <c r="B183" t="s">
+        <v>147</v>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="D183">
+        <v>3</v>
+      </c>
+      <c r="E183">
+        <v>0</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
+      <c r="A184" t="s">
+        <v>94</v>
+      </c>
+      <c r="B184" t="s">
+        <v>126</v>
+      </c>
+      <c r="C184">
+        <v>2</v>
+      </c>
+      <c r="D184">
+        <v>6</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
+      <c r="A185" t="s">
+        <v>94</v>
+      </c>
+      <c r="B185" t="s">
+        <v>153</v>
+      </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
+      <c r="D185">
+        <v>3</v>
+      </c>
+      <c r="E185">
+        <v>0</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="A186" t="s">
+        <v>94</v>
+      </c>
+      <c r="B186" t="s">
+        <v>124</v>
+      </c>
+      <c r="C186">
+        <v>2</v>
+      </c>
+      <c r="D186">
+        <v>3</v>
+      </c>
+      <c r="E186">
+        <v>0</v>
+      </c>
+      <c r="F186">
+        <v>1</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
+      <c r="A187" t="s">
+        <v>94</v>
+      </c>
+      <c r="B187" t="s">
+        <v>136</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187">
+        <v>3</v>
+      </c>
+      <c r="E187">
+        <v>0</v>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+      <c r="G187">
+        <v>0</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
+      <c r="A188" t="s">
+        <v>95</v>
+      </c>
+      <c r="B188" t="s">
+        <v>153</v>
+      </c>
+      <c r="C188">
+        <v>6</v>
+      </c>
+      <c r="D188">
+        <v>19</v>
+      </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+      <c r="G188">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
+      <c r="A189" t="s">
+        <v>95</v>
+      </c>
+      <c r="B189" t="s">
+        <v>147</v>
+      </c>
+      <c r="C189">
+        <v>2</v>
+      </c>
+      <c r="D189">
+        <v>5</v>
+      </c>
+      <c r="E189">
+        <v>0</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
+      <c r="A190" t="s">
+        <v>95</v>
+      </c>
+      <c r="B190" t="s">
+        <v>155</v>
+      </c>
+      <c r="C190">
+        <v>2</v>
+      </c>
+      <c r="D190">
+        <v>6</v>
+      </c>
+      <c r="E190">
+        <v>0</v>
+      </c>
+      <c r="F190">
+        <v>1</v>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
+      <c r="A191" t="s">
+        <v>95</v>
+      </c>
+      <c r="B191" t="s">
+        <v>155</v>
+      </c>
+      <c r="C191">
+        <v>2</v>
+      </c>
+      <c r="D191">
+        <v>6</v>
+      </c>
+      <c r="E191">
+        <v>0</v>
+      </c>
+      <c r="F191">
+        <v>1</v>
+      </c>
+      <c r="G191">
+        <v>0</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
+      <c r="A192" t="s">
+        <v>96</v>
+      </c>
+      <c r="B192" t="s">
+        <v>145</v>
+      </c>
+      <c r="C192">
+        <v>4</v>
+      </c>
+      <c r="D192">
+        <v>16</v>
+      </c>
+      <c r="E192">
+        <v>1</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="A193" t="s">
+        <v>95</v>
+      </c>
+      <c r="B193" t="s">
+        <v>153</v>
+      </c>
+      <c r="C193">
+        <v>5</v>
+      </c>
+      <c r="D193">
+        <v>25</v>
+      </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>1</v>
+      </c>
+      <c r="I193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" t="s">
+        <v>96</v>
+      </c>
+      <c r="B194" t="s">
+        <v>155</v>
+      </c>
+      <c r="C194">
+        <v>3</v>
+      </c>
+      <c r="D194">
+        <v>9</v>
+      </c>
+      <c r="E194">
+        <v>0</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="A195" t="s">
+        <v>96</v>
+      </c>
+      <c r="B195" t="s">
+        <v>124</v>
+      </c>
+      <c r="C195">
+        <v>3</v>
+      </c>
+      <c r="D195">
+        <v>12</v>
+      </c>
+      <c r="E195">
+        <v>1</v>
+      </c>
+      <c r="F195">
+        <v>1</v>
+      </c>
+      <c r="G195">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196" t="s">
+        <v>97</v>
+      </c>
+      <c r="B196" t="s">
+        <v>136</v>
+      </c>
+      <c r="C196">
+        <v>4</v>
+      </c>
+      <c r="D196">
+        <v>13</v>
+      </c>
+      <c r="E196">
+        <v>1</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+      <c r="G196">
+        <v>0</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197" t="s">
+        <v>97</v>
+      </c>
+      <c r="B197" t="s">
+        <v>120</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197">
+        <v>2</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
+      <c r="F197">
+        <v>1</v>
+      </c>
+      <c r="G197">
+        <v>0</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="A198" t="s">
+        <v>97</v>
+      </c>
+      <c r="B198" t="s">
+        <v>116</v>
+      </c>
+      <c r="C198">
+        <v>2</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198">
+        <v>0</v>
+      </c>
+      <c r="F198">
+        <v>1</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
+      <c r="A199" t="s">
+        <v>97</v>
+      </c>
+      <c r="B199" t="s">
+        <v>145</v>
+      </c>
+      <c r="C199">
+        <v>4</v>
+      </c>
+      <c r="D199">
+        <v>12</v>
+      </c>
+      <c r="E199">
+        <v>1</v>
+      </c>
+      <c r="F199">
+        <v>1</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
+      <c r="A200" t="s">
+        <v>97</v>
+      </c>
+      <c r="B200" t="s">
+        <v>153</v>
+      </c>
+      <c r="C200">
+        <v>8</v>
+      </c>
+      <c r="D200">
+        <v>24</v>
+      </c>
+      <c r="E200">
+        <v>1</v>
+      </c>
+      <c r="F200">
+        <v>1</v>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>1</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
+      <c r="A201" t="s">
+        <v>98</v>
+      </c>
+      <c r="B201" t="s">
+        <v>156</v>
+      </c>
+      <c r="C201">
+        <v>1</v>
+      </c>
+      <c r="D201">
+        <v>3</v>
+      </c>
+      <c r="E201">
+        <v>1</v>
+      </c>
+      <c r="F201">
+        <v>1</v>
+      </c>
+      <c r="G201">
+        <v>0</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
+      <c r="A202" t="s">
+        <v>98</v>
+      </c>
+      <c r="B202" t="s">
+        <v>121</v>
+      </c>
+      <c r="C202">
+        <v>1</v>
+      </c>
+      <c r="D202">
+        <v>3</v>
+      </c>
+      <c r="E202">
+        <v>1</v>
+      </c>
+      <c r="F202">
+        <v>1</v>
+      </c>
+      <c r="G202">
+        <v>1</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
+      <c r="A203" t="s">
+        <v>98</v>
+      </c>
+      <c r="B203" t="s">
+        <v>153</v>
+      </c>
+      <c r="C203">
+        <v>2</v>
+      </c>
+      <c r="D203">
+        <v>6</v>
+      </c>
+      <c r="E203">
+        <v>1</v>
+      </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
+      <c r="G203">
+        <v>0</v>
+      </c>
+      <c r="H203">
+        <v>1</v>
+      </c>
+      <c r="I203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="A204" t="s">
+        <v>99</v>
+      </c>
+      <c r="B204" t="s">
+        <v>157</v>
+      </c>
+      <c r="C204">
+        <v>23</v>
+      </c>
+      <c r="D204">
+        <v>45</v>
+      </c>
+      <c r="E204">
+        <v>3</v>
+      </c>
+      <c r="F204">
+        <v>2</v>
+      </c>
+      <c r="G204">
+        <v>1</v>
+      </c>
+      <c r="H204">
+        <v>1</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="A205" t="s">
+        <v>100</v>
+      </c>
+      <c r="B205" t="s">
+        <v>157</v>
+      </c>
+      <c r="C205">
+        <v>10</v>
+      </c>
+      <c r="D205">
+        <v>15</v>
+      </c>
+      <c r="E205">
+        <v>3</v>
+      </c>
+      <c r="F205">
+        <v>2</v>
+      </c>
+      <c r="G205">
+        <v>1</v>
+      </c>
+      <c r="H205">
+        <v>1</v>
+      </c>
+      <c r="I205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="A206" t="s">
+        <v>100</v>
+      </c>
+      <c r="B206" t="s">
+        <v>158</v>
+      </c>
+      <c r="C206">
+        <v>2</v>
+      </c>
+      <c r="D206">
+        <v>6</v>
+      </c>
+      <c r="E206">
+        <v>1</v>
+      </c>
+      <c r="F206">
+        <v>1</v>
+      </c>
+      <c r="G206">
+        <v>0</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="A207" t="s">
+        <v>100</v>
+      </c>
+      <c r="B207" t="s">
+        <v>131</v>
+      </c>
+      <c r="C207">
+        <v>2</v>
+      </c>
+      <c r="D207">
+        <v>6</v>
+      </c>
+      <c r="E207">
+        <v>1</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+      <c r="G207">
+        <v>0</v>
+      </c>
+      <c r="H207">
+        <v>0</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="A208" t="s">
+        <v>101</v>
+      </c>
+      <c r="B208" t="s">
+        <v>153</v>
+      </c>
+      <c r="C208">
+        <v>2</v>
+      </c>
+      <c r="D208">
+        <v>6</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+      <c r="F208">
+        <v>1</v>
+      </c>
+      <c r="G208">
+        <v>1</v>
+      </c>
+      <c r="H208">
+        <v>1</v>
+      </c>
+      <c r="I208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
+      <c r="A209" t="s">
+        <v>101</v>
+      </c>
+      <c r="B209" t="s">
+        <v>159</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="D209">
+        <v>4</v>
+      </c>
+      <c r="E209">
+        <v>1</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209">
+        <v>0</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
+      <c r="A210" t="s">
+        <v>102</v>
+      </c>
+      <c r="B210" t="s">
+        <v>160</v>
+      </c>
+      <c r="C210">
+        <v>3</v>
+      </c>
+      <c r="D210">
+        <v>9</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210">
+        <v>1</v>
+      </c>
+      <c r="G210">
+        <v>1</v>
+      </c>
+      <c r="H210">
+        <v>1</v>
+      </c>
+      <c r="I210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
+      <c r="A211" t="s">
+        <v>102</v>
+      </c>
+      <c r="B211" t="s">
+        <v>161</v>
+      </c>
+      <c r="C211">
+        <v>4</v>
+      </c>
+      <c r="D211">
+        <v>9</v>
+      </c>
+      <c r="E211">
+        <v>1</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+      <c r="G211">
+        <v>0</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
+      <c r="A212" t="s">
+        <v>102</v>
+      </c>
+      <c r="B212" t="s">
+        <v>160</v>
+      </c>
+      <c r="C212">
+        <v>2</v>
+      </c>
+      <c r="D212">
+        <v>7</v>
+      </c>
+      <c r="E212">
+        <v>0</v>
+      </c>
+      <c r="F212">
+        <v>1</v>
+      </c>
+      <c r="G212">
+        <v>1</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
+      <c r="A213" t="s">
+        <v>103</v>
+      </c>
+      <c r="B213" t="s">
+        <v>121</v>
+      </c>
+      <c r="C213">
+        <v>4</v>
+      </c>
+      <c r="D213">
+        <v>12</v>
+      </c>
+      <c r="E213">
+        <v>1</v>
+      </c>
+      <c r="F213">
+        <v>1</v>
+      </c>
+      <c r="G213">
+        <v>1</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
+      <c r="A214" t="s">
+        <v>103</v>
+      </c>
+      <c r="B214" t="s">
+        <v>145</v>
+      </c>
+      <c r="C214">
+        <v>2</v>
+      </c>
+      <c r="D214">
+        <v>6</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+      <c r="F214">
+        <v>1</v>
+      </c>
+      <c r="G214">
+        <v>1</v>
+      </c>
+      <c r="H214">
+        <v>1</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
+      <c r="A215" t="s">
+        <v>104</v>
+      </c>
+      <c r="B215" t="s">
+        <v>162</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="D215">
+        <v>5</v>
+      </c>
+      <c r="E215">
+        <v>1</v>
+      </c>
+      <c r="F215">
+        <v>1</v>
+      </c>
+      <c r="G215">
+        <v>0</v>
+      </c>
+      <c r="H215">
+        <v>1</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
+      <c r="A216" t="s">
+        <v>104</v>
+      </c>
+      <c r="B216" t="s">
+        <v>130</v>
+      </c>
+      <c r="C216">
+        <v>2</v>
+      </c>
+      <c r="D216">
+        <v>5</v>
+      </c>
+      <c r="E216">
+        <v>1</v>
+      </c>
+      <c r="F216">
+        <v>1</v>
+      </c>
+      <c r="G216">
+        <v>0</v>
+      </c>
+      <c r="H216">
+        <v>0</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
+      <c r="A217" t="s">
+        <v>104</v>
+      </c>
+      <c r="B217" t="s">
+        <v>137</v>
+      </c>
+      <c r="C217">
+        <v>2</v>
+      </c>
+      <c r="D217">
+        <v>7</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+      <c r="G217">
+        <v>0</v>
+      </c>
+      <c r="H217">
+        <v>1</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
+      <c r="A218" t="s">
+        <v>105</v>
+      </c>
+      <c r="B218" t="s">
+        <v>131</v>
+      </c>
+      <c r="C218">
+        <v>2</v>
+      </c>
+      <c r="D218">
+        <v>6</v>
+      </c>
+      <c r="E218">
+        <v>1</v>
+      </c>
+      <c r="F218">
+        <v>1</v>
+      </c>
+      <c r="G218">
+        <v>0</v>
+      </c>
+      <c r="H218">
+        <v>1</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
+      <c r="A219" t="s">
+        <v>106</v>
+      </c>
+      <c r="B219" t="s">
+        <v>163</v>
+      </c>
+      <c r="C219">
+        <v>9</v>
+      </c>
+      <c r="D219">
+        <v>24</v>
+      </c>
+      <c r="E219">
+        <v>2</v>
+      </c>
+      <c r="F219">
+        <v>1</v>
+      </c>
+      <c r="G219">
+        <v>1</v>
+      </c>
+      <c r="H219">
+        <v>1</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
+      <c r="A220" t="s">
+        <v>106</v>
+      </c>
+      <c r="B220" t="s">
+        <v>141</v>
+      </c>
+      <c r="C220">
+        <v>2</v>
+      </c>
+      <c r="D220">
+        <v>6</v>
+      </c>
+      <c r="E220">
+        <v>1</v>
+      </c>
+      <c r="F220">
+        <v>1</v>
+      </c>
+      <c r="G220">
+        <v>1</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
+      <c r="A221" t="s">
+        <v>106</v>
+      </c>
+      <c r="B221" t="s">
+        <v>151</v>
+      </c>
+      <c r="C221">
+        <v>1</v>
+      </c>
+      <c r="D221">
+        <v>3</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
+      <c r="F221">
+        <v>1</v>
+      </c>
+      <c r="G221">
+        <v>0</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
+      <c r="A222" t="s">
+        <v>106</v>
+      </c>
+      <c r="B222" t="s">
+        <v>162</v>
+      </c>
+      <c r="C222">
+        <v>2</v>
+      </c>
+      <c r="D222">
+        <v>6</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222">
+        <v>0</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
+      <c r="A223" t="s">
+        <v>106</v>
+      </c>
+      <c r="B223" t="s">
+        <v>129</v>
+      </c>
+      <c r="C223">
+        <v>2</v>
+      </c>
+      <c r="D223">
+        <v>6</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
+      </c>
+      <c r="G223">
+        <v>0</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
+      <c r="A224" t="s">
+        <v>107</v>
+      </c>
+      <c r="B224" t="s">
+        <v>163</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+      <c r="D224">
+        <v>3</v>
+      </c>
+      <c r="E224">
+        <v>0</v>
+      </c>
+      <c r="F224">
+        <v>1</v>
+      </c>
+      <c r="G224">
+        <v>1</v>
+      </c>
+      <c r="H224">
+        <v>1</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
+      <c r="A225" t="s">
+        <v>108</v>
+      </c>
+      <c r="B225" t="s">
+        <v>121</v>
+      </c>
+      <c r="C225">
+        <v>3</v>
+      </c>
+      <c r="D225">
+        <v>9</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+      <c r="F225">
+        <v>1</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
+      <c r="A226" t="s">
+        <v>108</v>
+      </c>
+      <c r="B226" t="s">
+        <v>130</v>
+      </c>
+      <c r="C226">
+        <v>2</v>
+      </c>
+      <c r="D226">
+        <v>6</v>
+      </c>
+      <c r="E226">
+        <v>0</v>
+      </c>
+      <c r="F226">
+        <v>1</v>
+      </c>
+      <c r="G226">
+        <v>0</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
+      <c r="A227" t="s">
+        <v>108</v>
+      </c>
+      <c r="B227" t="s">
+        <v>141</v>
+      </c>
+      <c r="C227">
+        <v>1</v>
+      </c>
+      <c r="D227">
+        <v>3</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
+      <c r="F227">
+        <v>1</v>
+      </c>
+      <c r="G227">
+        <v>0</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
+      <c r="A228" t="s">
+        <v>109</v>
+      </c>
+      <c r="B228" t="s">
+        <v>164</v>
+      </c>
+      <c r="C228">
+        <v>1</v>
+      </c>
+      <c r="D228">
+        <v>3</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+      <c r="F228">
+        <v>1</v>
+      </c>
+      <c r="G228">
+        <v>1</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
+      <c r="A229" t="s">
+        <v>109</v>
+      </c>
+      <c r="B229" t="s">
+        <v>165</v>
+      </c>
+      <c r="C229">
+        <v>1</v>
+      </c>
+      <c r="D229">
+        <v>3</v>
+      </c>
+      <c r="E229">
+        <v>1</v>
+      </c>
+      <c r="F229">
+        <v>1</v>
+      </c>
+      <c r="G229">
+        <v>0</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
+      <c r="A230" t="s">
+        <v>109</v>
+      </c>
+      <c r="B230" t="s">
+        <v>166</v>
+      </c>
+      <c r="C230">
+        <v>2</v>
+      </c>
+      <c r="D230">
+        <v>11</v>
+      </c>
+      <c r="E230">
+        <v>1</v>
+      </c>
+      <c r="F230">
+        <v>1</v>
+      </c>
+      <c r="G230">
+        <v>1</v>
+      </c>
+      <c r="H230">
+        <v>1</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
+      <c r="A231" t="s">
+        <v>109</v>
+      </c>
+      <c r="B231" t="s">
+        <v>121</v>
+      </c>
+      <c r="C231">
+        <v>1</v>
+      </c>
+      <c r="D231">
+        <v>3</v>
+      </c>
+      <c r="E231">
+        <v>0</v>
+      </c>
+      <c r="F231">
+        <v>1</v>
+      </c>
+      <c r="G231">
+        <v>0</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
+      <c r="A232" t="s">
+        <v>110</v>
+      </c>
+      <c r="B232" t="s">
+        <v>166</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+      <c r="D232">
+        <v>3</v>
+      </c>
+      <c r="E232">
+        <v>1</v>
+      </c>
+      <c r="F232">
+        <v>1</v>
+      </c>
+      <c r="G232">
+        <v>0</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
+      <c r="A233" t="s">
+        <v>111</v>
+      </c>
+      <c r="B233" t="s">
+        <v>129</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+      <c r="D233">
+        <v>3</v>
+      </c>
+      <c r="E233">
+        <v>1</v>
+      </c>
+      <c r="F233">
+        <v>1</v>
+      </c>
+      <c r="G233">
+        <v>0</v>
+      </c>
+      <c r="H233">
+        <v>0</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
+      <c r="A234" t="s">
+        <v>111</v>
+      </c>
+      <c r="B234" t="s">
+        <v>162</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+      <c r="D234">
+        <v>3</v>
+      </c>
+      <c r="E234">
+        <v>0</v>
+      </c>
+      <c r="F234">
+        <v>1</v>
+      </c>
+      <c r="G234">
+        <v>0</v>
+      </c>
+      <c r="H234">
+        <v>0</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
+      <c r="A235" t="s">
+        <v>112</v>
+      </c>
+      <c r="B235" t="s">
+        <v>130</v>
+      </c>
+      <c r="C235" t="s">
+        <v>167</v>
+      </c>
+      <c r="D235" t="s">
+        <v>168</v>
+      </c>
+      <c r="E235" t="s">
+        <v>169</v>
+      </c>
+      <c r="F235" t="s">
+        <v>169</v>
+      </c>
+      <c r="G235" t="s">
+        <v>170</v>
+      </c>
+      <c r="H235" t="s">
+        <v>170</v>
+      </c>
+      <c r="I235" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
